--- a/data/scheduled_interviews.xlsx
+++ b/data/scheduled_interviews.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,64 +463,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pooja Mehta</t>
+          <t>Anita Verma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>smc9182444@gmail.com</t>
+          <t>yashwanth9182444@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>frontend developer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30-01-2026 10:30 AM</t>
+          <t>09-03-2026 07:50 PM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8-9 LPA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pooja_Mehta_CA7eba34182a18490d35ce60db3d7426e9.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>yashwanthdevangam@gmail.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>27-01-2026 07:23 PM</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>9.5 lakhs per annum</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rahul_Sharma_CA6842dda0579702dbfe942212d4251a5c.txt</t>
+          <t>Anita_Verma_CA3de64f1fc265387947d07ed3342b0751.txt</t>
         </is>
       </c>
     </row>

--- a/data/scheduled_interviews.xlsx
+++ b/data/scheduled_interviews.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09-03-2026 07:50 PM</t>
+          <t>09-03-2026 07:00 PM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
